--- a/timetable_generator/timetable_outputs/CSE_Sem3_SectionB_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/CSE_Sem3_SectionB_Timetable.xlsx
@@ -467,7 +467,10 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>CS261
 Operating Sytems
@@ -475,16 +478,6 @@
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CS263
-Design and analysis of algorithm 
-C101
-Dr. Promod Y</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,7 +486,8 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>CS264
 Computer networks 
@@ -501,16 +495,8 @@
 Dr. Prabhu Prasad</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CS263
-Design and analysis of algorithm 
-C101
-Dr. Promod Y</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,7 +505,8 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>CS263
 Design and analysis of algorithm 
@@ -527,14 +514,13 @@
 Dr. Promod Y</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS261
-Operating Sytems
-C101
-Dr. Suvadip Hazra</t>
+          <t>CA262
+Software design tools and tehniques
+C101
+Dr. Vivekraj</t>
         </is>
       </c>
     </row>
@@ -546,22 +532,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>CS263
+Design and analysis of algorithm 
+C101
+Dr. Promod Y</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>CA262
 Software design tools and tehniques
 C101
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CA262
-Software design tools and tehniques
-C101
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CS264
+Computer networks 
+C101
+Dr. Prabhu Prasad</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CS261
+Operating Sytems
+C101
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -570,25 +570,26 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CS264
+Computer networks 
+C101
+Dr. Prabhu Prasad
+[TUTORIAL]</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS264
-Computer networks 
-C101
-Dr. Prabhu Prasad</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CS264
-Computer networks 
-C101
-Dr. Prabhu Prasad</t>
-        </is>
-      </c>
+          <t>CS263
+Design and analysis of algorithm 
+C101
+Dr. Promod Y</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
